--- a/takenrooster.xlsx
+++ b/takenrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Projects\Volleybal\Wedstrijdrooster 6.0.0\Wedstrijdrooster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{5BFB87FD-03DB-4076-9D9D-99F37A5BC370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E752A62-44A7-4D2D-AAF1-A0E838B9286C}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{5BFB87FD-03DB-4076-9D9D-99F37A5BC370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7ABC561-92EE-4F00-920F-06CBB3FFCBFC}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-4905" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="318">
   <si>
     <t>vnr</t>
   </si>
@@ -199,12 +199,18 @@
     <t>Shot HS 2</t>
   </si>
   <si>
+    <t>HS3</t>
+  </si>
+  <si>
     <t>BD1B27CB</t>
   </si>
   <si>
     <t>USV Protos DS 5</t>
   </si>
   <si>
+    <t>DS3</t>
+  </si>
+  <si>
     <t>JA2C1 DE</t>
   </si>
   <si>
@@ -223,6 +229,9 @@
     <t>scheidsrechter (VSB)</t>
   </si>
   <si>
+    <t>XR1</t>
+  </si>
+  <si>
     <t>BD1B28CD</t>
   </si>
   <si>
@@ -259,9 +268,21 @@
     <t>Taurus HR 1</t>
   </si>
   <si>
+    <t>Sander van der Spek</t>
+  </si>
+  <si>
+    <t>XR2</t>
+  </si>
+  <si>
+    <t>JA1</t>
+  </si>
+  <si>
     <t>DS 3, HS 1, HS 2, XR 2</t>
   </si>
   <si>
+    <t>MA1</t>
+  </si>
+  <si>
     <t>D2P   BI</t>
   </si>
   <si>
@@ -277,6 +298,9 @@
     <t>VV Utrecht JA 4</t>
   </si>
   <si>
+    <t>DS1</t>
+  </si>
+  <si>
     <t>MB2J1 AB</t>
   </si>
   <si>
@@ -319,6 +343,9 @@
     <t>De Valk MA 1</t>
   </si>
   <si>
+    <t>DS2</t>
+  </si>
+  <si>
     <t>HPD   HB</t>
   </si>
   <si>
@@ -346,6 +373,9 @@
     <t>HR 2, HS 1, XR 1</t>
   </si>
   <si>
+    <t>HS2</t>
+  </si>
+  <si>
     <t>D4G   AH</t>
   </si>
   <si>
@@ -361,6 +391,9 @@
     <t>VIVES DS 8</t>
   </si>
   <si>
+    <t>MB1</t>
+  </si>
+  <si>
     <t>JA2C1 DC</t>
   </si>
   <si>
@@ -473,6 +506,9 @@
   </si>
   <si>
     <t>DOS HS 3</t>
+  </si>
+  <si>
+    <t>VERVALT</t>
   </si>
   <si>
     <t>DS 1, DS 3, HS 2</t>
@@ -1005,7 +1041,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1900,7 +1936,7 @@
       <c r="P4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="17"/>
+      <c r="Q4" s="29"/>
       <c r="R4" s="29"/>
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
@@ -2004,10 +2040,10 @@
       <c r="P6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17" t="s">
+      <c r="Q6" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="R6" s="17"/>
       <c r="S6" s="17" t="s">
         <v>39</v>
       </c>
@@ -2062,10 +2098,10 @@
       <c r="P7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17" t="s">
+      <c r="Q7" s="17" t="s">
         <v>38</v>
       </c>
+      <c r="R7" s="17"/>
       <c r="S7" s="17" t="s">
         <v>41</v>
       </c>
@@ -2172,8 +2208,8 @@
       <c r="P9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
       <c r="S9" s="17"/>
       <c r="T9" s="17" t="s">
         <v>40</v>
@@ -2224,8 +2260,8 @@
       <c r="P10" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
       <c r="S10" s="17"/>
       <c r="T10" s="17" t="s">
         <v>40</v>
@@ -2276,7 +2312,9 @@
       <c r="P11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="17"/>
+      <c r="Q11" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
       <c r="T11" s="17" t="s">
@@ -2299,7 +2337,7 @@
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>21</v>
@@ -2311,7 +2349,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L12" s="22">
         <v>3</v>
@@ -2328,8 +2366,8 @@
       <c r="P12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
       <c r="S12" s="17"/>
       <c r="T12" s="17" t="s">
         <v>40</v>
@@ -2351,7 +2389,7 @@
       </c>
       <c r="F13" s="21"/>
       <c r="G13" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>21</v>
@@ -2363,7 +2401,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L13" s="22">
         <v>3</v>
@@ -2380,7 +2418,9 @@
       <c r="P13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17" t="s">
+        <v>54</v>
+      </c>
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
       <c r="T13" s="17" t="s">
@@ -2403,19 +2443,19 @@
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L14" s="22">
         <v>4</v>
@@ -2430,9 +2470,11 @@
         <v>27</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q14" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
       <c r="T14" s="17" t="s">
@@ -2455,19 +2497,19 @@
       </c>
       <c r="F15" s="27"/>
       <c r="G15" s="23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L15" s="28">
         <v>4</v>
@@ -2484,7 +2526,9 @@
       <c r="P15" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="23"/>
+      <c r="Q15" s="23" t="s">
+        <v>61</v>
+      </c>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
       <c r="T15" s="23" t="s">
@@ -2507,19 +2551,19 @@
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J16" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L16" s="22">
         <v>2</v>
@@ -2561,19 +2605,19 @@
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L17" s="28">
         <v>2</v>
@@ -2590,7 +2634,9 @@
       <c r="P17" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q17" s="23"/>
+      <c r="Q17" s="23" t="s">
+        <v>54</v>
+      </c>
       <c r="R17" s="23"/>
       <c r="S17" s="23"/>
       <c r="T17" s="23" t="s">
@@ -2613,7 +2659,7 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>43</v>
@@ -2625,7 +2671,7 @@
         <v>45</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L18" s="22">
         <v>1</v>
@@ -2642,7 +2688,9 @@
       <c r="P18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="17"/>
+      <c r="Q18" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="R18" s="30"/>
       <c r="S18" s="17"/>
       <c r="T18" s="17" t="s">
@@ -2665,7 +2713,7 @@
       </c>
       <c r="F19" s="21"/>
       <c r="G19" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>43</v>
@@ -2677,7 +2725,7 @@
         <v>45</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L19" s="22">
         <v>1</v>
@@ -2694,8 +2742,8 @@
       <c r="P19" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
       <c r="S19" s="17"/>
       <c r="T19" s="17" t="s">
         <v>35</v>
@@ -2717,19 +2765,19 @@
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L20" s="22">
         <v>3</v>
@@ -2744,10 +2792,12 @@
         <v>27</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
+      <c r="R20" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="S20" s="17"/>
       <c r="T20" s="17" t="s">
         <v>35</v>
@@ -2769,19 +2819,19 @@
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L21" s="28">
         <v>3</v>
@@ -2798,7 +2848,9 @@
       <c r="P21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q21" s="23"/>
+      <c r="Q21" s="23" t="s">
+        <v>75</v>
+      </c>
       <c r="R21" s="23"/>
       <c r="S21" s="23"/>
       <c r="T21" s="23" t="s">
@@ -2852,11 +2904,15 @@
       <c r="P22" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q22" s="17"/>
+      <c r="Q22" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
+      <c r="S22" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="T22" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="11.25">
@@ -2906,11 +2962,15 @@
       <c r="P23" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q23" s="17"/>
+      <c r="Q23" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
+      <c r="S23" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="T23" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="11.25">
@@ -2929,19 +2989,19 @@
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="17" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L24" s="22">
         <v>1</v>
@@ -2958,11 +3018,11 @@
       <c r="P24" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
       <c r="S24" s="17"/>
       <c r="T24" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="11.25">
@@ -2981,19 +3041,19 @@
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="17" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L25" s="22">
         <v>1</v>
@@ -3010,11 +3070,13 @@
       <c r="P25" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q25" s="17"/>
+      <c r="Q25" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
       <c r="T25" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="11.25">
@@ -3033,19 +3095,19 @@
       </c>
       <c r="F26" s="21"/>
       <c r="G26" s="17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L26" s="22">
         <v>2</v>
@@ -3060,13 +3122,15 @@
         <v>27</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q26" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
       <c r="T26" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="11.25">
@@ -3085,19 +3149,19 @@
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L27" s="22">
         <v>2</v>
@@ -3114,11 +3178,13 @@
       <c r="P27" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q27" s="17"/>
+      <c r="Q27" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R27" s="17"/>
       <c r="S27" s="17"/>
       <c r="T27" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="11.25">
@@ -3137,19 +3203,19 @@
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="17" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L28" s="22">
         <v>3</v>
@@ -3164,13 +3230,15 @@
         <v>27</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q28" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q28" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R28" s="17"/>
       <c r="S28" s="17"/>
       <c r="T28" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="11.25">
@@ -3189,19 +3257,19 @@
       </c>
       <c r="F29" s="21"/>
       <c r="G29" s="17" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="L29" s="22">
         <v>3</v>
@@ -3218,11 +3286,13 @@
       <c r="P29" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q29" s="17"/>
+      <c r="Q29" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R29" s="17"/>
       <c r="S29" s="17"/>
       <c r="T29" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="11.25">
@@ -3241,19 +3311,19 @@
       </c>
       <c r="F30" s="21"/>
       <c r="G30" s="17" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L30" s="22">
         <v>1</v>
@@ -3276,7 +3346,7 @@
       </c>
       <c r="S30" s="17"/>
       <c r="T30" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="11.25">
@@ -3295,19 +3365,19 @@
       </c>
       <c r="F31" s="21"/>
       <c r="G31" s="17" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L31" s="22">
         <v>1</v>
@@ -3324,11 +3394,13 @@
       <c r="P31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="17"/>
+      <c r="Q31" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
       <c r="T31" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="11.25">
@@ -3347,19 +3419,19 @@
       </c>
       <c r="F32" s="21"/>
       <c r="G32" s="17" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="L32" s="22">
         <v>2</v>
@@ -3374,13 +3446,15 @@
         <v>27</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q32" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q32" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
       <c r="T32" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="13" customFormat="1" ht="11.25">
@@ -3399,19 +3473,19 @@
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="23" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="L33" s="28">
         <v>2</v>
@@ -3428,11 +3502,13 @@
       <c r="P33" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q33" s="23"/>
+      <c r="Q33" s="23" t="s">
+        <v>99</v>
+      </c>
       <c r="R33" s="23"/>
       <c r="S33" s="23"/>
       <c r="T33" s="23" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="11.25">
@@ -3451,19 +3527,19 @@
       </c>
       <c r="F34" s="21"/>
       <c r="G34" s="17" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="L34" s="22">
         <v>1</v>
@@ -3503,19 +3579,19 @@
       </c>
       <c r="F35" s="21"/>
       <c r="G35" s="17" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J35" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="L35" s="22">
         <v>1</v>
@@ -3532,8 +3608,8 @@
       <c r="P35" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
     </row>
@@ -3553,19 +3629,19 @@
       </c>
       <c r="F36" s="21"/>
       <c r="G36" s="17" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L36" s="22">
         <v>3</v>
@@ -3580,10 +3656,12 @@
         <v>27</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
+      <c r="R36" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="S36" s="17"/>
       <c r="T36" s="17"/>
     </row>
@@ -3603,19 +3681,19 @@
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J37" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L37" s="28">
         <v>3</v>
@@ -3632,7 +3710,9 @@
       <c r="P37" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q37" s="23"/>
+      <c r="Q37" s="23" t="s">
+        <v>61</v>
+      </c>
       <c r="R37" s="23"/>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
@@ -3684,11 +3764,13 @@
       <c r="P38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q38" s="17"/>
+      <c r="Q38" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="R38" s="17"/>
       <c r="S38" s="17"/>
       <c r="T38" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="11.25">
@@ -3738,11 +3820,13 @@
       <c r="P39" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q39" s="17"/>
+      <c r="Q39" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R39" s="17"/>
       <c r="S39" s="17"/>
       <c r="T39" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="11.25">
@@ -3761,19 +3845,19 @@
       </c>
       <c r="F40" s="21"/>
       <c r="G40" s="17" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L40" s="22">
         <v>1</v>
@@ -3788,13 +3872,15 @@
         <v>27</v>
       </c>
       <c r="P40" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q40" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q40" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R40" s="17"/>
       <c r="S40" s="17"/>
       <c r="T40" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="11.25">
@@ -3813,19 +3899,19 @@
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="17" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L41" s="22">
         <v>1</v>
@@ -3842,11 +3928,13 @@
       <c r="P41" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q41" s="17"/>
+      <c r="Q41" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R41" s="17"/>
       <c r="S41" s="17"/>
       <c r="T41" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="11.25">
@@ -3865,19 +3953,19 @@
       </c>
       <c r="F42" s="21"/>
       <c r="G42" s="17" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="L42" s="22">
         <v>2</v>
@@ -3892,13 +3980,15 @@
         <v>27</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
+      <c r="R42" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="S42" s="17"/>
       <c r="T42" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:20" ht="11.25">
@@ -3917,19 +4007,19 @@
       </c>
       <c r="F43" s="21"/>
       <c r="G43" s="17" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="L43" s="22">
         <v>2</v>
@@ -3946,11 +4036,13 @@
       <c r="P43" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q43" s="17"/>
+      <c r="Q43" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R43" s="17"/>
       <c r="S43" s="17"/>
       <c r="T43" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:20" ht="11.25">
@@ -3969,19 +4061,19 @@
       </c>
       <c r="F44" s="21"/>
       <c r="G44" s="17" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L44" s="22">
         <v>3</v>
@@ -3996,13 +4088,15 @@
         <v>27</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q44" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q44" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R44" s="17"/>
       <c r="S44" s="17"/>
       <c r="T44" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="11.25">
@@ -4021,19 +4115,19 @@
       </c>
       <c r="F45" s="21"/>
       <c r="G45" s="17" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L45" s="22">
         <v>3</v>
@@ -4050,11 +4144,13 @@
       <c r="P45" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q45" s="17"/>
+      <c r="Q45" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R45" s="17"/>
       <c r="S45" s="17"/>
       <c r="T45" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:20" ht="11.25">
@@ -4073,19 +4169,19 @@
       </c>
       <c r="F46" s="21"/>
       <c r="G46" s="17" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L46" s="22">
         <v>1</v>
@@ -4102,11 +4198,11 @@
       <c r="P46" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
       <c r="S46" s="17"/>
       <c r="T46" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="11.25">
@@ -4125,19 +4221,19 @@
       </c>
       <c r="F47" s="21"/>
       <c r="G47" s="17" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J47" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K47" s="17" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L47" s="22">
         <v>1</v>
@@ -4154,11 +4250,13 @@
       <c r="P47" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q47" s="17"/>
+      <c r="Q47" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R47" s="17"/>
       <c r="S47" s="17"/>
       <c r="T47" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:20" ht="11.25">
@@ -4177,19 +4275,19 @@
       </c>
       <c r="F48" s="21"/>
       <c r="G48" s="17" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="L48" s="22">
         <v>2</v>
@@ -4204,13 +4302,15 @@
         <v>27</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q48" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q48" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R48" s="17"/>
       <c r="S48" s="17"/>
       <c r="T48" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="11.25">
@@ -4229,19 +4329,19 @@
       </c>
       <c r="F49" s="21"/>
       <c r="G49" s="17" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="L49" s="22">
         <v>2</v>
@@ -4258,11 +4358,13 @@
       <c r="P49" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q49" s="17"/>
+      <c r="Q49" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R49" s="17"/>
       <c r="S49" s="17"/>
       <c r="T49" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="11.25">
@@ -4281,19 +4383,19 @@
       </c>
       <c r="F50" s="21"/>
       <c r="G50" s="17" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J50" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="L50" s="22">
         <v>1</v>
@@ -4310,11 +4412,11 @@
       <c r="P50" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
       <c r="S50" s="17"/>
       <c r="T50" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="11.25">
@@ -4333,19 +4435,19 @@
       </c>
       <c r="F51" s="21"/>
       <c r="G51" s="17" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J51" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="L51" s="22">
         <v>1</v>
@@ -4362,11 +4464,13 @@
       <c r="P51" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q51" s="17"/>
+      <c r="Q51" s="17" t="s">
+        <v>75</v>
+      </c>
       <c r="R51" s="17"/>
       <c r="S51" s="17"/>
       <c r="T51" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="11.25">
@@ -4385,19 +4489,19 @@
       </c>
       <c r="F52" s="21"/>
       <c r="G52" s="17" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="L52" s="22">
         <v>2</v>
@@ -4414,11 +4518,11 @@
       <c r="P52" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
       <c r="S52" s="17"/>
       <c r="T52" s="17" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:20" s="13" customFormat="1" ht="11.25">
@@ -4437,19 +4541,19 @@
       </c>
       <c r="F53" s="27"/>
       <c r="G53" s="23" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J53" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K53" s="23" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="L53" s="28">
         <v>2</v>
@@ -4466,11 +4570,13 @@
       <c r="P53" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q53" s="23"/>
+      <c r="Q53" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="R53" s="23"/>
       <c r="S53" s="23"/>
       <c r="T53" s="23" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="11.25">
@@ -4489,19 +4595,19 @@
       </c>
       <c r="F54" s="21"/>
       <c r="G54" s="17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J54" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L54" s="22">
         <v>2</v>
@@ -4516,9 +4622,11 @@
         <v>27</v>
       </c>
       <c r="P54" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q54" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q54" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R54" s="17"/>
       <c r="S54" s="17"/>
       <c r="T54" s="17"/>
@@ -4539,19 +4647,19 @@
       </c>
       <c r="F55" s="27"/>
       <c r="G55" s="23" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I55" s="23" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J55" s="23" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K55" s="23" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L55" s="28">
         <v>2</v>
@@ -4568,7 +4676,9 @@
       <c r="P55" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q55" s="23"/>
+      <c r="Q55" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
       <c r="T55" s="23"/>
@@ -4589,19 +4699,19 @@
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="17" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J56" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L56" s="22">
         <v>1</v>
@@ -4641,19 +4751,19 @@
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="17" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J57" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K57" s="17" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L57" s="22">
         <v>1</v>
@@ -4670,8 +4780,8 @@
       <c r="P57" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
       <c r="S57" s="17"/>
       <c r="T57" s="17"/>
     </row>
@@ -4691,19 +4801,19 @@
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="17" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J58" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L58" s="22">
         <v>3</v>
@@ -4718,10 +4828,12 @@
         <v>27</v>
       </c>
       <c r="P58" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
+      <c r="R58" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="S58" s="17"/>
       <c r="T58" s="17"/>
     </row>
@@ -4741,19 +4853,19 @@
       </c>
       <c r="F59" s="27"/>
       <c r="G59" s="23" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J59" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K59" s="23" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L59" s="28">
         <v>3</v>
@@ -4770,7 +4882,9 @@
       <c r="P59" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q59" s="23"/>
+      <c r="Q59" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="R59" s="23"/>
       <c r="S59" s="23"/>
       <c r="T59" s="23"/>
@@ -4822,9 +4936,13 @@
       <c r="P60" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q60" s="17"/>
+      <c r="Q60" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
+      <c r="S60" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="T60" s="17"/>
     </row>
     <row r="61" spans="1:20" ht="11.25">
@@ -4874,9 +4992,13 @@
       <c r="P61" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q61" s="17"/>
+      <c r="Q61" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
+      <c r="S61" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="T61" s="17"/>
     </row>
     <row r="62" spans="1:20" ht="11.25">
@@ -4895,19 +5017,19 @@
       </c>
       <c r="F62" s="21"/>
       <c r="G62" s="17" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J62" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L62" s="22">
         <v>3</v>
@@ -4922,9 +5044,11 @@
         <v>27</v>
       </c>
       <c r="P62" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q62" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q62" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="T62" s="17"/>
@@ -4945,19 +5069,19 @@
       </c>
       <c r="F63" s="21"/>
       <c r="G63" s="17" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J63" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="L63" s="22">
         <v>3</v>
@@ -4974,7 +5098,9 @@
       <c r="P63" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q63" s="17"/>
+      <c r="Q63" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="R63" s="17"/>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
@@ -4995,19 +5121,19 @@
       </c>
       <c r="F64" s="21"/>
       <c r="G64" s="17" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J64" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K64" s="17" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L64" s="22">
         <v>1</v>
@@ -5024,8 +5150,8 @@
       <c r="P64" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
       <c r="S64" s="17"/>
       <c r="T64" s="17"/>
     </row>
@@ -5045,19 +5171,19 @@
       </c>
       <c r="F65" s="21"/>
       <c r="G65" s="17" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J65" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L65" s="22">
         <v>1</v>
@@ -5074,7 +5200,9 @@
       <c r="P65" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q65" s="17"/>
+      <c r="Q65" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R65" s="17"/>
       <c r="S65" s="17"/>
       <c r="T65" s="17"/>
@@ -5095,19 +5223,19 @@
       </c>
       <c r="F66" s="21"/>
       <c r="G66" s="17" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J66" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L66" s="22">
         <v>2</v>
@@ -5122,9 +5250,11 @@
         <v>27</v>
       </c>
       <c r="P66" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q66" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q66" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R66" s="17"/>
       <c r="S66" s="17"/>
       <c r="T66" s="17"/>
@@ -5145,19 +5275,19 @@
       </c>
       <c r="F67" s="21"/>
       <c r="G67" s="17" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="L67" s="22">
         <v>2</v>
@@ -5174,7 +5304,9 @@
       <c r="P67" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q67" s="17"/>
+      <c r="Q67" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R67" s="17"/>
       <c r="S67" s="17"/>
       <c r="T67" s="17"/>
@@ -5195,19 +5327,19 @@
       </c>
       <c r="F68" s="21"/>
       <c r="G68" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J68" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L68" s="22">
         <v>3</v>
@@ -5222,9 +5354,11 @@
         <v>27</v>
       </c>
       <c r="P68" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q68" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q68" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R68" s="17"/>
       <c r="S68" s="17"/>
       <c r="T68" s="17"/>
@@ -5245,19 +5379,19 @@
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J69" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K69" s="17" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="L69" s="22">
         <v>3</v>
@@ -5274,7 +5408,9 @@
       <c r="P69" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q69" s="17"/>
+      <c r="Q69" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R69" s="17"/>
       <c r="S69" s="17"/>
       <c r="T69" s="17"/>
@@ -5295,19 +5431,19 @@
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="17" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J70" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K70" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="L70" s="22">
         <v>1</v>
@@ -5347,19 +5483,19 @@
       </c>
       <c r="F71" s="21"/>
       <c r="G71" s="17" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J71" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K71" s="17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="L71" s="22">
         <v>1</v>
@@ -5376,7 +5512,9 @@
       <c r="P71" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q71" s="17"/>
+      <c r="Q71" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R71" s="17"/>
       <c r="S71" s="17"/>
       <c r="T71" s="17"/>
@@ -5397,19 +5535,19 @@
       </c>
       <c r="F72" s="21"/>
       <c r="G72" s="17" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J72" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K72" s="17" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L72" s="22">
         <v>2</v>
@@ -5426,8 +5564,8 @@
       <c r="P72" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17"/>
+      <c r="Q72" s="29"/>
+      <c r="R72" s="29"/>
       <c r="S72" s="17"/>
       <c r="T72" s="17"/>
     </row>
@@ -5447,19 +5585,19 @@
       </c>
       <c r="F73" s="21"/>
       <c r="G73" s="17" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J73" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K73" s="17" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="L73" s="22">
         <v>2</v>
@@ -5476,7 +5614,9 @@
       <c r="P73" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q73" s="17"/>
+      <c r="Q73" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
       <c r="T73" s="17"/>
@@ -5497,19 +5637,19 @@
       </c>
       <c r="F74" s="21"/>
       <c r="G74" s="17" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J74" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K74" s="17" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="L74" s="22">
         <v>3</v>
@@ -5524,9 +5664,11 @@
         <v>27</v>
       </c>
       <c r="P74" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q74" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q74" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
       <c r="T74" s="17"/>
@@ -5547,19 +5689,19 @@
       </c>
       <c r="F75" s="21"/>
       <c r="G75" s="17" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J75" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K75" s="17" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="L75" s="22">
         <v>3</v>
@@ -5576,7 +5718,9 @@
       <c r="P75" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q75" s="17"/>
+      <c r="Q75" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
       <c r="T75" s="17"/>
@@ -5597,19 +5741,19 @@
       </c>
       <c r="F76" s="21"/>
       <c r="G76" s="17" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J76" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K76" s="17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L76" s="22">
         <v>1</v>
@@ -5649,19 +5793,19 @@
       </c>
       <c r="F77" s="21"/>
       <c r="G77" s="17" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J77" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="L77" s="22">
         <v>1</v>
@@ -5678,8 +5822,8 @@
       <c r="P77" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="17"/>
+      <c r="Q77" s="29"/>
+      <c r="R77" s="29"/>
       <c r="S77" s="17"/>
       <c r="T77" s="17"/>
     </row>
@@ -5699,19 +5843,19 @@
       </c>
       <c r="F78" s="21"/>
       <c r="G78" s="17" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K78" s="17" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L78" s="22">
         <v>2</v>
@@ -5726,9 +5870,11 @@
         <v>27</v>
       </c>
       <c r="P78" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q78" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q78" s="17" t="s">
+        <v>54</v>
+      </c>
       <c r="R78" s="17"/>
       <c r="S78" s="17"/>
       <c r="T78" s="17"/>
@@ -5749,19 +5895,19 @@
       </c>
       <c r="F79" s="27"/>
       <c r="G79" s="23" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H79" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K79" s="23" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L79" s="28">
         <v>2</v>
@@ -5778,7 +5924,9 @@
       <c r="P79" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q79" s="23"/>
+      <c r="Q79" s="23" t="s">
+        <v>109</v>
+      </c>
       <c r="R79" s="23"/>
       <c r="S79" s="23"/>
       <c r="T79" s="23"/>
@@ -5831,10 +5979,14 @@
         <v>37</v>
       </c>
       <c r="Q80" s="17"/>
-      <c r="R80" s="17"/>
-      <c r="S80" s="17"/>
+      <c r="R80" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="S80" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="T80" s="17" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:20" s="13" customFormat="1" ht="11.25">
@@ -5885,10 +6037,14 @@
         <v>37</v>
       </c>
       <c r="Q81" s="23"/>
-      <c r="R81" s="23"/>
-      <c r="S81" s="23"/>
+      <c r="R81" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="S81" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="T81" s="23" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" spans="1:20" ht="11.25">
@@ -5938,9 +6094,13 @@
       <c r="P82" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q82" s="17"/>
+      <c r="Q82" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R82" s="17"/>
-      <c r="S82" s="17"/>
+      <c r="S82" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="T82" s="17"/>
     </row>
     <row r="83" spans="1:20" ht="11.25">
@@ -5990,9 +6150,13 @@
       <c r="P83" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q83" s="17"/>
+      <c r="Q83" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R83" s="17"/>
-      <c r="S83" s="17"/>
+      <c r="S83" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="T83" s="17"/>
     </row>
     <row r="84" spans="1:20" ht="11.25">
@@ -6011,19 +6175,19 @@
       </c>
       <c r="F84" s="21"/>
       <c r="G84" s="17" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H84" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K84" s="17" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="L84" s="22">
         <v>2</v>
@@ -6038,9 +6202,11 @@
         <v>27</v>
       </c>
       <c r="P84" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q84" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q84" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R84" s="17"/>
       <c r="S84" s="17"/>
       <c r="T84" s="17"/>
@@ -6061,19 +6227,19 @@
       </c>
       <c r="F85" s="21"/>
       <c r="G85" s="17" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K85" s="17" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="L85" s="22">
         <v>2</v>
@@ -6090,7 +6256,9 @@
       <c r="P85" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q85" s="17"/>
+      <c r="Q85" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
       <c r="T85" s="17"/>
@@ -6111,19 +6279,19 @@
       </c>
       <c r="F86" s="21"/>
       <c r="G86" s="17" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K86" s="17" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="L86" s="22">
         <v>1</v>
@@ -6138,9 +6306,11 @@
         <v>27</v>
       </c>
       <c r="P86" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q86" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q86" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
       <c r="T86" s="17"/>
@@ -6161,19 +6331,19 @@
       </c>
       <c r="F87" s="21"/>
       <c r="G87" s="17" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="L87" s="22">
         <v>1</v>
@@ -6190,7 +6360,9 @@
       <c r="P87" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q87" s="17"/>
+      <c r="Q87" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R87" s="17"/>
       <c r="S87" s="17"/>
       <c r="T87" s="17"/>
@@ -6211,19 +6383,19 @@
       </c>
       <c r="F88" s="21"/>
       <c r="G88" s="17" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="L88" s="22">
         <v>2</v>
@@ -6238,9 +6410,11 @@
         <v>27</v>
       </c>
       <c r="P88" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q88" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q88" s="17" t="s">
+        <v>54</v>
+      </c>
       <c r="R88" s="17"/>
       <c r="S88" s="17"/>
       <c r="T88" s="17"/>
@@ -6261,19 +6435,19 @@
       </c>
       <c r="F89" s="21"/>
       <c r="G89" s="17" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="L89" s="22">
         <v>2</v>
@@ -6290,7 +6464,9 @@
       <c r="P89" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q89" s="17"/>
+      <c r="Q89" s="17" t="s">
+        <v>115</v>
+      </c>
       <c r="R89" s="17"/>
       <c r="S89" s="17"/>
       <c r="T89" s="17"/>
@@ -6311,19 +6487,19 @@
       </c>
       <c r="F90" s="21"/>
       <c r="G90" s="17" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J90" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K90" s="17" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="L90" s="22">
         <v>3</v>
@@ -6338,9 +6514,11 @@
         <v>27</v>
       </c>
       <c r="P90" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q90" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q90" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R90" s="17"/>
       <c r="S90" s="17"/>
       <c r="T90" s="17"/>
@@ -6361,19 +6539,19 @@
       </c>
       <c r="F91" s="21"/>
       <c r="G91" s="17" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="L91" s="22">
         <v>3</v>
@@ -6390,7 +6568,9 @@
       <c r="P91" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q91" s="17"/>
+      <c r="Q91" s="17" t="s">
+        <v>84</v>
+      </c>
       <c r="R91" s="17"/>
       <c r="S91" s="17"/>
       <c r="T91" s="17"/>
@@ -6411,19 +6591,19 @@
       </c>
       <c r="F92" s="21"/>
       <c r="G92" s="17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J92" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L92" s="22">
         <v>1</v>
@@ -6463,19 +6643,19 @@
       </c>
       <c r="F93" s="21"/>
       <c r="G93" s="17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J93" s="17" t="s">
         <v>23</v>
       </c>
       <c r="K93" s="17" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L93" s="22">
         <v>1</v>
@@ -6492,7 +6672,9 @@
       <c r="P93" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q93" s="17"/>
+      <c r="Q93" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R93" s="17"/>
       <c r="S93" s="17"/>
       <c r="T93" s="17"/>
@@ -6513,19 +6695,19 @@
       </c>
       <c r="F94" s="21"/>
       <c r="G94" s="17" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J94" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="L94" s="22">
         <v>2</v>
@@ -6542,8 +6724,8 @@
       <c r="P94" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q94" s="17"/>
-      <c r="R94" s="17"/>
+      <c r="Q94" s="29"/>
+      <c r="R94" s="29"/>
       <c r="S94" s="17"/>
       <c r="T94" s="17"/>
     </row>
@@ -6563,19 +6745,19 @@
       </c>
       <c r="F95" s="21"/>
       <c r="G95" s="17" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J95" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K95" s="17" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="L95" s="22">
         <v>2</v>
@@ -6592,7 +6774,9 @@
       <c r="P95" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q95" s="17"/>
+      <c r="Q95" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R95" s="17"/>
       <c r="S95" s="17"/>
       <c r="T95" s="17"/>
@@ -6613,19 +6797,19 @@
       </c>
       <c r="F96" s="21"/>
       <c r="G96" s="17" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K96" s="17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L96" s="22">
         <v>3</v>
@@ -6640,9 +6824,11 @@
         <v>27</v>
       </c>
       <c r="P96" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q96" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="Q96" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="R96" s="17"/>
       <c r="S96" s="17"/>
       <c r="T96" s="17"/>
@@ -6663,19 +6849,19 @@
       </c>
       <c r="F97" s="21"/>
       <c r="G97" s="17" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L97" s="22">
         <v>3</v>
@@ -6692,7 +6878,9 @@
       <c r="P97" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q97" s="17"/>
+      <c r="Q97" s="17" t="s">
+        <v>78</v>
+      </c>
       <c r="R97" s="17"/>
       <c r="S97" s="17"/>
       <c r="T97" s="17"/>
@@ -6713,19 +6901,19 @@
       </c>
       <c r="F98" s="21"/>
       <c r="G98" s="17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="L98" s="22">
         <v>1</v>
@@ -6765,19 +6953,19 @@
       </c>
       <c r="F99" s="21"/>
       <c r="G99" s="17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J99" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="L99" s="22">
         <v>1</v>
@@ -6794,8 +6982,8 @@
       <c r="P99" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q99" s="17"/>
-      <c r="R99" s="17"/>
+      <c r="Q99" s="29"/>
+      <c r="R99" s="29"/>
       <c r="S99" s="17"/>
       <c r="T99" s="17"/>
     </row>
@@ -6815,19 +7003,19 @@
       </c>
       <c r="F100" s="21"/>
       <c r="G100" s="17" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K100" s="17" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L100" s="22">
         <v>2</v>
@@ -6844,8 +7032,8 @@
       <c r="P100" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q100" s="17"/>
-      <c r="R100" s="17"/>
+      <c r="Q100" s="29"/>
+      <c r="R100" s="29"/>
       <c r="S100" s="17"/>
       <c r="T100" s="17"/>
     </row>
@@ -6865,19 +7053,19 @@
       </c>
       <c r="F101" s="27"/>
       <c r="G101" s="23" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I101" s="23" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J101" s="23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K101" s="23" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="L101" s="28">
         <v>2</v>
@@ -6894,7 +7082,9 @@
       <c r="P101" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="Q101" s="23"/>
+      <c r="Q101" s="23" t="s">
+        <v>54</v>
+      </c>
       <c r="R101" s="23"/>
       <c r="S101" s="23"/>
       <c r="T101" s="23"/>
@@ -6946,11 +7136,15 @@
       <c r="P102" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q102" s="17"/>
+      <c r="Q102" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="R102" s="17"/>
-      <c r="S102" s="17"/>
+      <c r="S102" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="T102" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="11.25">
@@ -7000,11 +7194,15 @@
       <c r="P103" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q103" s="17"/>
+      <c r="Q103" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="R103" s="17"/>
-      <c r="S103" s="17"/>
+      <c r="S103" s="17" t="s">
+        <v>41</v>
+      </c>
       <c r="T103" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="11.25">
@@ -7023,19 +7221,19 @@
       </c>
       <c r="F104" s="21"/>
       <c r="G104" s="17" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J104" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K104" s="17" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L104" s="22">
         <v>1</v>
@@ -7058,7 +7256,7 @@
       </c>
       <c r="S104" s="17"/>
       <c r="T104" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="11.25">
@@ -7077,19 +7275,19 @@
       </c>
       <c r="F105" s="21"/>
       <c r="G105" s="17" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J105" s="17" t="s">
         <v>45</v>
       </c>
       <c r="K105" s="17" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L105" s="22">
         <v>1</v>
@@ -7106,11 +7304,11 @@
       <c r="P105" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="Q105" s="17"/>
-      <c r="R105" s="17"/>
+      <c r="Q105" s="29"/>
+      <c r="R105" s="29"/>
       <c r="S105" s="17"/>
       <c r="T105" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="11.25">
@@ -7129,19 +7327,19 @@
       </c>
       <c r="F106" s="21"/>
       <c r="G106" s="17" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J106" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K106" s="17" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="L106" s="22">
         <v>2</v>
@@ -7158,11 +7356,11 @@
       <c r="P106" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="Q106" s="17"/>
-      <c r="R106" s="17"/>
+      <c r="Q106" s="29"/>
+      <c r="R106" s="29"/>
       <c r="S106" s="17"/>
       <c r="T106" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="11.25">
@@ -7181,19 +7379,19 @@
       </c>
       <c r="F107" s="21"/>
       <c r="G107" s="17" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="J107" s="17" t="s">
         <v>35</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="L107" s="22">
         <v>2</v>
@@ -7210,11 +7408,13 @@
       <c r="P107" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q107" s="17"/>
+      <c r="Q107" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="R107" s="17"/>
       <c r="S107" s="17"/>
       <c r="T107" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="11.25">
@@ -7233,19 +7433,19 @@
       </c>
       <c r="F108" s="21"/>
       <c r="G108" s="17" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J108" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L108" s="22">
         <v>3</v>
@@ -7260,13 +7460,15 @@
         <v>27</v>
       </c>
       <c r="P108" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q108" s="17"/>
-      <c r="R108" s="17"/>
+      <c r="R108" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="S108" s="17"/>
       <c r="T108" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="11.25">
@@ -7285,19 +7487,19 @@
       </c>
       <c r="F109" s="21"/>
       <c r="G109" s="17" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="L109" s="22">
         <v>3</v>
@@ -7314,11 +7516,13 @@
       <c r="P109" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q109" s="17"/>
+      <c r="Q109" s="17" t="s">
+        <v>75</v>
+      </c>
       <c r="R109" s="17"/>
       <c r="S109" s="17"/>
       <c r="T109" s="17" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -7394,16 +7598,16 @@
         <v>46270.479166666701</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="13" customFormat="1">
@@ -7420,16 +7624,16 @@
         <v>46272.916666666701</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="13" customFormat="1">
@@ -7446,16 +7650,16 @@
         <v>46276.791666666701</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -7472,16 +7676,16 @@
         <v>46277.4375</v>
       </c>
       <c r="F5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I5" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="13" customFormat="1">
@@ -7498,16 +7702,16 @@
         <v>46277.604166666701</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1">
@@ -7524,16 +7728,16 @@
         <v>46279.833333333299</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="G7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1">
@@ -7550,16 +7754,16 @@
         <v>46282.854166666701</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -7576,16 +7780,16 @@
         <v>46283.791666666701</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H9" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="I9" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1">
@@ -7602,16 +7806,16 @@
         <v>46283.895833333299</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -7628,16 +7832,16 @@
         <v>46284.375</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G11" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H11" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="I11" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -7654,16 +7858,16 @@
         <v>46284.458333333299</v>
       </c>
       <c r="F12" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H12" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="I12" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1">
@@ -7680,16 +7884,16 @@
         <v>46284.666666666701</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>45</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="13" customFormat="1">
@@ -7706,16 +7910,16 @@
         <v>46290.84375</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -7732,16 +7936,16 @@
         <v>46291.583333333299</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G15" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H15" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I15" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -7758,16 +7962,16 @@
         <v>46291.625</v>
       </c>
       <c r="F16" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G16" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H16" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -7784,16 +7988,16 @@
         <v>46291.645833333299</v>
       </c>
       <c r="F17" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G17" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I17" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -7810,16 +8014,16 @@
         <v>46291.6875</v>
       </c>
       <c r="F18" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G18" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H18" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I18" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -7836,16 +8040,16 @@
         <v>46291.6875</v>
       </c>
       <c r="F19" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="G19" t="s">
         <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="I19" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -7862,16 +8066,16 @@
         <v>46291.458333333299</v>
       </c>
       <c r="F20" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I20" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="13" customFormat="1">
@@ -7888,16 +8092,16 @@
         <v>46291.739583333299</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -7914,16 +8118,16 @@
         <v>46297.770833333299</v>
       </c>
       <c r="F22" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H22" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="I22" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="13" customFormat="1">
@@ -7940,16 +8144,16 @@
         <v>46297.833333333299</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -7966,16 +8170,16 @@
         <v>46298.583333333299</v>
       </c>
       <c r="F24" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G24" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H24" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I24" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -7992,16 +8196,16 @@
         <v>46298.458333333299</v>
       </c>
       <c r="F25" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H25" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="I25" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -8018,16 +8222,16 @@
         <v>46298.458333333299</v>
       </c>
       <c r="F26" t="s">
+        <v>234</v>
+      </c>
+      <c r="G26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" t="s">
+        <v>235</v>
+      </c>
+      <c r="I26" t="s">
         <v>222</v>
-      </c>
-      <c r="G26" t="s">
-        <v>103</v>
-      </c>
-      <c r="H26" t="s">
-        <v>223</v>
-      </c>
-      <c r="I26" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -8044,16 +8248,16 @@
         <v>46298.458333333299</v>
       </c>
       <c r="F27" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="G27" t="s">
         <v>35</v>
       </c>
       <c r="H27" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="I27" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -8070,16 +8274,16 @@
         <v>46298.479166666701</v>
       </c>
       <c r="F28" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="13" customFormat="1">
@@ -8096,16 +8300,16 @@
         <v>46298.59375</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="13" customFormat="1">
@@ -8122,16 +8326,16 @@
         <v>46304.895833333299</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -8148,16 +8352,16 @@
         <v>46305.666666666701</v>
       </c>
       <c r="F31" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="G31" t="s">
         <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I31" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -8174,16 +8378,16 @@
         <v>46305.541666666701</v>
       </c>
       <c r="F32" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G32" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -8200,16 +8404,16 @@
         <v>46305.583333333299</v>
       </c>
       <c r="F33" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G33" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H33" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I33" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -8226,16 +8430,16 @@
         <v>46305.625</v>
       </c>
       <c r="F34" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="G34" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H34" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I34" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -8252,16 +8456,16 @@
         <v>46305.6875</v>
       </c>
       <c r="F35" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G35" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H35" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I35" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -8278,16 +8482,16 @@
         <v>46305.479166666701</v>
       </c>
       <c r="F36" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="G36" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H36" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I36" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -8304,16 +8508,16 @@
         <v>46305.520833333299</v>
       </c>
       <c r="F37" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="G37" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H37" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I37" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -8330,16 +8534,16 @@
         <v>46305.5625</v>
       </c>
       <c r="F38" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="G38" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H38" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I38" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="13" customFormat="1">
@@ -8356,16 +8560,16 @@
         <v>46305.625</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="13" customFormat="1">
@@ -8382,16 +8586,16 @@
         <v>46311.895833333299</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -8408,16 +8612,16 @@
         <v>46312.520833333299</v>
       </c>
       <c r="F41" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G41" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H41" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="I41" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -8434,16 +8638,16 @@
         <v>46312.833333333299</v>
       </c>
       <c r="F42" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G42" t="s">
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I42" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="13" customFormat="1">
@@ -8460,16 +8664,16 @@
         <v>46312.59375</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="13" customFormat="1">
@@ -8486,16 +8690,16 @@
         <v>46319.604166666701</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="13" customFormat="1">
@@ -8512,16 +8716,16 @@
         <v>46323.895833333299</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="13" customFormat="1">
@@ -8538,16 +8742,16 @@
         <v>46325.895833333299</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -8564,16 +8768,16 @@
         <v>46326.583333333299</v>
       </c>
       <c r="F47" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
       </c>
       <c r="H47" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I47" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -8590,16 +8794,16 @@
         <v>46326.520833333299</v>
       </c>
       <c r="F48" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I48" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="13" customFormat="1">
@@ -8616,16 +8820,16 @@
         <v>46326.604166666701</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -8642,16 +8846,16 @@
         <v>46340.583333333299</v>
       </c>
       <c r="F50" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="G50" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H50" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="I50" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -8668,16 +8872,16 @@
         <v>46340.520833333299</v>
       </c>
       <c r="F51" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
       </c>
       <c r="H51" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I51" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="13" customFormat="1">
@@ -8694,16 +8898,16 @@
         <v>46340.541666666701</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>35</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -8720,16 +8924,16 @@
         <v>46353.833333333299</v>
       </c>
       <c r="F53" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="G53" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H53" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="I53" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="13" customFormat="1">
@@ -8746,16 +8950,16 @@
         <v>46353.8125</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -8772,16 +8976,16 @@
         <v>46354.5625</v>
       </c>
       <c r="F55" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="G55" t="s">
         <v>23</v>
       </c>
       <c r="H55" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I55" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -8798,16 +9002,16 @@
         <v>46354.666666666701</v>
       </c>
       <c r="F56" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G56" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H56" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I56" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -8824,16 +9028,16 @@
         <v>46354.6875</v>
       </c>
       <c r="F57" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="G57" t="s">
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="I57" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -8850,16 +9054,16 @@
         <v>46354.520833333299</v>
       </c>
       <c r="F58" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H58" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I58" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -8876,16 +9080,16 @@
         <v>46354.375</v>
       </c>
       <c r="F59" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H59" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="I59" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="13" customFormat="1">
@@ -8902,16 +9106,16 @@
         <v>46354.458333333299</v>
       </c>
       <c r="F60" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="I60" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="13" customFormat="1">
@@ -8928,16 +9132,16 @@
         <v>46363.854166666701</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -8954,16 +9158,16 @@
         <v>46368.5</v>
       </c>
       <c r="F62" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G62" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="I62" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -8980,16 +9184,16 @@
         <v>46368.541666666701</v>
       </c>
       <c r="F63" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="G63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H63" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="I63" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -9006,16 +9210,16 @@
         <v>46368.395833333299</v>
       </c>
       <c r="F64" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="G64" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H64" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="I64" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -9032,16 +9236,16 @@
         <v>46368.458333333299</v>
       </c>
       <c r="F65" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="G65" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H65" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="I65" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -9058,16 +9262,16 @@
         <v>46368.5</v>
       </c>
       <c r="F66" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G66" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H66" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="I66" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -9084,16 +9288,16 @@
         <v>46368.541666666701</v>
       </c>
       <c r="F67" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="G67" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="H67" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="I67" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -9110,16 +9314,16 @@
         <v>46368.375</v>
       </c>
       <c r="F68" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="I68" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="13" customFormat="1">
@@ -9136,16 +9340,16 @@
         <v>46368.625</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -9162,16 +9366,16 @@
         <v>46375.541666666701</v>
       </c>
       <c r="F70" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G70" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H70" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I70" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -9188,16 +9392,16 @@
         <v>46375.604166666701</v>
       </c>
       <c r="F71" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G71" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H71" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I71" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -9214,16 +9418,16 @@
         <v>46375.645833333299</v>
       </c>
       <c r="F72" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="G72" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H72" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I72" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -9240,16 +9444,16 @@
         <v>46375.6875</v>
       </c>
       <c r="F73" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="G73" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H73" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="I73" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -9266,16 +9470,16 @@
         <v>46375.604166666701</v>
       </c>
       <c r="F74" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="G74" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H74" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I74" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -9292,16 +9496,16 @@
         <v>46375.645833333299</v>
       </c>
       <c r="F75" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="G75" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H75" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I75" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -9318,16 +9522,16 @@
         <v>46375.6875</v>
       </c>
       <c r="F76" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="G76" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H76" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I76" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -9344,16 +9548,16 @@
         <v>46375.708333333299</v>
       </c>
       <c r="F77" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="G77" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="H77" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I77" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
